--- a/data/trans_camb/IP19C01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 24,54</t>
+          <t>-0,34; 25,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 17,09</t>
+          <t>-8,83; 18,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 30,03</t>
+          <t>4,58; 30,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 9,09</t>
+          <t>-17,58; 6,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 20,29</t>
+          <t>-2,13; 20,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 26,96</t>
+          <t>3,3; 26,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 13,08</t>
+          <t>-4,11; 12,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 15,61</t>
+          <t>-1,58; 16,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 24,97</t>
+          <t>8,4; 25,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 44,54</t>
+          <t>-0,08; 47,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 30,31</t>
+          <t>-13,16; 32,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 54,89</t>
+          <t>7,36; 56,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 14,87</t>
+          <t>-23,16; 10,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 32,09</t>
+          <t>-2,39; 32,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 42,41</t>
+          <t>5,25; 41,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 20,84</t>
+          <t>-5,82; 21,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 25,01</t>
+          <t>-2,29; 25,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,19; 40,78</t>
+          <t>12,11; 41,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 6,76</t>
+          <t>-13,54; 6,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 12,63</t>
+          <t>-7,82; 12,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 27,9</t>
+          <t>10,02; 28,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 15,74</t>
+          <t>-3,63; 14,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 9,27</t>
+          <t>-10,49; 9,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 16,01</t>
+          <t>-3,15; 14,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 8,05</t>
+          <t>-5,39; 8,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,72</t>
+          <t>-6,26; 7,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 18,27</t>
+          <t>4,97; 17,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 10,86</t>
+          <t>-18,57; 10,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 20,34</t>
+          <t>-11,03; 20,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 45,09</t>
+          <t>14,54; 45,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 23,29</t>
+          <t>-4,34; 22,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 13,97</t>
+          <t>-13,53; 13,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 23,87</t>
+          <t>-3,97; 21,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 12,11</t>
+          <t>-7,37; 12,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 10,06</t>
+          <t>-8,5; 11,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 27,3</t>
+          <t>6,93; 26,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 15,1</t>
+          <t>-8,9; 14,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 18,53</t>
+          <t>-4,52; 17,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 12,19</t>
+          <t>-11,66; 11,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 9,89</t>
+          <t>-12,25; 10,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 9,89</t>
+          <t>-11,08; 10,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 17,45</t>
+          <t>-3,85; 17,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 9,14</t>
+          <t>-6,56; 9,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 11,68</t>
+          <t>-5,06; 10,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 11,21</t>
+          <t>-5,16; 11,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 23,56</t>
+          <t>-11,52; 22,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 29,27</t>
+          <t>-5,86; 26,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 18,77</t>
+          <t>-15,55; 18,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 14,77</t>
+          <t>-15,91; 15,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 14,95</t>
+          <t>-14,41; 14,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 26,25</t>
+          <t>-4,71; 27,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 13,08</t>
+          <t>-8,65; 13,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 17,3</t>
+          <t>-6,57; 15,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 16,18</t>
+          <t>-6,91; 16,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 25,0</t>
+          <t>1,47; 24,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 25,77</t>
+          <t>4,68; 25,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,69; 33,24</t>
+          <t>13,68; 33,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 24,8</t>
+          <t>3,25; 24,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 20,04</t>
+          <t>0,36; 20,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,98; 28,57</t>
+          <t>7,33; 26,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 20,74</t>
+          <t>6,68; 21,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 20,37</t>
+          <t>5,96; 21,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,28; 28,26</t>
+          <t>13,05; 28,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,73; 46,26</t>
+          <t>2,23; 42,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 45,87</t>
+          <t>7,34; 47,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,92; 59,59</t>
+          <t>20,07; 60,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,59; 40,97</t>
+          <t>4,69; 39,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 33,57</t>
+          <t>0,37; 32,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 47,23</t>
+          <t>9,77; 43,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 33,91</t>
+          <t>9,5; 35,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,19; 33,19</t>
+          <t>8,18; 34,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,0; 46,73</t>
+          <t>18,29; 46,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 11,17</t>
+          <t>0,94; 11,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 13,36</t>
+          <t>1,86; 13,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,71</t>
+          <t>10,16; 20,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,78</t>
+          <t>-0,4; 9,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,83</t>
+          <t>-0,88; 9,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 16,33</t>
+          <t>5,54; 16,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,07</t>
+          <t>1,05; 8,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,7</t>
+          <t>2,0; 9,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,37; 16,91</t>
+          <t>9,47; 17,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,7</t>
+          <t>1,38; 17,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,95; 21,28</t>
+          <t>2,62; 21,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,47; 32,73</t>
+          <t>14,49; 32,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 14,23</t>
+          <t>-0,52; 14,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 14,53</t>
+          <t>-1,19; 13,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,84; 23,68</t>
+          <t>7,55; 23,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,51</t>
+          <t>1,47; 13,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,59</t>
+          <t>2,83; 14,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,29</t>
+          <t>13,51; 25,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 25,12</t>
+          <t>-1,59; 23,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 18,15</t>
+          <t>-9,23; 16,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 30,58</t>
+          <t>6,82; 31,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 6,89</t>
+          <t>-16,95; 7,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 20,55</t>
+          <t>-2,25; 19,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 26,25</t>
+          <t>4,19; 27,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 12,65</t>
+          <t>-3,88; 12,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 16,06</t>
+          <t>-1,53; 16,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 25,15</t>
+          <t>9,2; 25,96</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 47,6</t>
+          <t>-2,31; 41,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 32,46</t>
+          <t>-12,91; 30,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 56,09</t>
+          <t>10,47; 57,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 10,44</t>
+          <t>-23,1; 11,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 32,56</t>
+          <t>-3,08; 30,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 41,5</t>
+          <t>5,57; 43,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 21,02</t>
+          <t>-5,73; 20,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 25,58</t>
+          <t>-2,02; 26,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 41,8</t>
+          <t>13,06; 41,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 6,57</t>
+          <t>-12,82; 6,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 12,56</t>
+          <t>-7,69; 11,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,02; 28,05</t>
+          <t>9,74; 27,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 14,41</t>
+          <t>-2,86; 15,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 9,1</t>
+          <t>-10,0; 9,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 14,72</t>
+          <t>-3,63; 14,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 8,08</t>
+          <t>-5,08; 8,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 7,69</t>
+          <t>-5,73; 7,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 17,55</t>
+          <t>4,96; 17,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 10,38</t>
+          <t>-17,76; 10,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 20,08</t>
+          <t>-10,72; 19,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,54; 45,52</t>
+          <t>13,5; 44,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 22,31</t>
+          <t>-3,78; 22,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 13,73</t>
+          <t>-13,05; 14,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 21,78</t>
+          <t>-4,71; 21,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 12,27</t>
+          <t>-6,84; 12,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 11,46</t>
+          <t>-7,93; 11,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 26,4</t>
+          <t>6,7; 27,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 14,39</t>
+          <t>-8,14; 15,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 17,54</t>
+          <t>-4,64; 17,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 11,72</t>
+          <t>-13,5; 12,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 10,38</t>
+          <t>-12,05; 9,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 10,25</t>
+          <t>-11,9; 10,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 17,9</t>
+          <t>-3,29; 18,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 9,25</t>
+          <t>-6,27; 9,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 10,78</t>
+          <t>-5,36; 10,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 11,43</t>
+          <t>-4,59; 11,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 22,84</t>
+          <t>-10,41; 23,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 26,59</t>
+          <t>-5,88; 26,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 18,57</t>
+          <t>-17,26; 19,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 15,4</t>
+          <t>-15,3; 14,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 14,97</t>
+          <t>-15,23; 16,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 27,13</t>
+          <t>-4,45; 28,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 13,43</t>
+          <t>-8,63; 13,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 15,78</t>
+          <t>-6,93; 15,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 16,98</t>
+          <t>-6,01; 16,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 24,03</t>
+          <t>0,81; 23,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 25,63</t>
+          <t>4,26; 26,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,68; 33,48</t>
+          <t>12,77; 34,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 24,03</t>
+          <t>3,34; 24,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 20,43</t>
+          <t>0,45; 21,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 26,96</t>
+          <t>7,64; 26,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 21,74</t>
+          <t>5,8; 21,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 21,05</t>
+          <t>5,69; 20,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,05; 28,19</t>
+          <t>13,61; 28,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 42,11</t>
+          <t>1,13; 41,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 47,33</t>
+          <t>5,96; 47,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,07; 60,35</t>
+          <t>19,13; 63,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 39,08</t>
+          <t>4,32; 38,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 32,83</t>
+          <t>0,6; 35,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,77; 43,19</t>
+          <t>10,09; 42,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,5; 35,94</t>
+          <t>8,08; 35,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,18; 34,29</t>
+          <t>8,34; 33,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,29; 46,27</t>
+          <t>19,36; 47,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,22</t>
+          <t>0,74; 11,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 13,3</t>
+          <t>1,68; 13,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,16; 20,82</t>
+          <t>9,77; 20,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,88</t>
+          <t>-0,91; 9,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 9,63</t>
+          <t>-1,17; 9,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,54; 16,09</t>
+          <t>5,61; 16,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,78</t>
+          <t>1,54; 9,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,95</t>
+          <t>2,4; 10,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,47; 17,08</t>
+          <t>9,6; 17,11</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,38; 17,72</t>
+          <t>1,16; 18,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,62; 21,13</t>
+          <t>2,48; 20,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,49; 32,87</t>
+          <t>14,21; 33,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,62</t>
+          <t>-1,24; 14,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 13,99</t>
+          <t>-1,58; 14,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,55; 23,58</t>
+          <t>7,54; 23,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,1</t>
+          <t>2,15; 14,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,96</t>
+          <t>3,39; 15,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,51; 25,81</t>
+          <t>13,78; 25,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,33</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18,53</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,92</t>
+          <t>18,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,33</t>
+          <t>17,59</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 23,51</t>
+          <t>-15,22; 9,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 16,54</t>
+          <t>-1,02; 20,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 31,15</t>
+          <t>5,23; 27,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 7,15</t>
+          <t>-0,08; 24,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 19,46</t>
+          <t>-9,25; 17,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 27,6</t>
+          <t>5,09; 30,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 12,58</t>
+          <t>-4,26; 13,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 16,09</t>
+          <t>-1,41; 15,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 25,96</t>
+          <t>9,24; 25,05</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-6,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>20,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 41,44</t>
+          <t>-20,17; 14,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 30,78</t>
+          <t>-1,38; 32,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 57,73</t>
+          <t>6,82; 42,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 11,24</t>
+          <t>0,37; 44,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 30,21</t>
+          <t>-13,64; 30,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 43,0</t>
+          <t>7,42; 55,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 20,02</t>
+          <t>-6,37; 20,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 26,24</t>
+          <t>-2,14; 25,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,06; 41,98</t>
+          <t>13,37; 40,7</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,94</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,34</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,99</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>18,72</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>11,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 6,72</t>
+          <t>-3,73; 15,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 11,99</t>
+          <t>-10,61; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,74; 27,26</t>
+          <t>-2,27; 16,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 15,28</t>
+          <t>-13,19; 6,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 9,59</t>
+          <t>-7,62; 12,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 14,5</t>
+          <t>8,5; 27,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 8,47</t>
+          <t>-5,24; 8,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 7,48</t>
+          <t>-6,85; 6,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 17,95</t>
+          <t>5,59; 18,39</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-4,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28,07%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 10,6</t>
+          <t>-4,66; 23,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 19,23</t>
+          <t>-13,76; 13,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 44,7</t>
+          <t>-2,92; 24,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 22,34</t>
+          <t>-18,17; 10,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 14,07</t>
+          <t>-10,48; 20,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 21,37</t>
+          <t>12,55; 44,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 12,73</t>
+          <t>-7,2; 12,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 11,18</t>
+          <t>-9,3; 10,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 27,25</t>
+          <t>7,68; 27,69</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,01</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,58</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>6,57</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>3,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 15,17</t>
+          <t>-12,85; 9,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 17,54</t>
+          <t>-12,84; 9,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 12,62</t>
+          <t>-6,5; 16,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 9,7</t>
+          <t>-7,89; 15,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 10,72</t>
+          <t>-4,45; 18,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 18,81</t>
+          <t>-11,97; 11,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,45</t>
+          <t>-6,63; 9,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 10,42</t>
+          <t>-5,14; 11,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 11,28</t>
+          <t>-5,28; 10,89</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-1,29%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-1,39%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9,18%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-0,08%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,29%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-1,39%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 23,77</t>
+          <t>-16,17; 14,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 26,96</t>
+          <t>-16,24; 14,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 19,95</t>
+          <t>-8,34; 24,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 14,61</t>
+          <t>-10,36; 23,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 16,2</t>
+          <t>-5,53; 29,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 28,05</t>
+          <t>-15,19; 18,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 13,73</t>
+          <t>-8,68; 13,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 15,34</t>
+          <t>-6,75; 17,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 16,48</t>
+          <t>-6,96; 15,82</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14,59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18,76</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12,7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>15,13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23,82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14,59</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,45</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,97</t>
+          <t>23,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20,98</t>
+          <t>21,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 23,68</t>
+          <t>5,64; 24,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 26,28</t>
+          <t>0,21; 20,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,77; 34,13</t>
+          <t>9,05; 29,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 24,88</t>
+          <t>2,49; 25,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 21,56</t>
+          <t>3,85; 25,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 26,9</t>
+          <t>12,4; 33,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 21,55</t>
+          <t>5,45; 20,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 20,41</t>
+          <t>5,05; 20,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,61; 28,55</t>
+          <t>14,75; 28,7</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15,1%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>20,02%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>23,84%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 41,62</t>
+          <t>7,59; 40,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 47,95</t>
+          <t>0,38; 33,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,13; 63,42</t>
+          <t>12,27; 47,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 38,99</t>
+          <t>3,73; 46,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 35,1</t>
+          <t>5,51; 45,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,09; 42,58</t>
+          <t>17,61; 59,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,08; 35,41</t>
+          <t>8,17; 33,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 33,37</t>
+          <t>7,19; 33,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,36; 47,08</t>
+          <t>20,55; 47,32</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11,17</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,96</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>7,4</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 11,59</t>
+          <t>-1,05; 9,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 13,02</t>
+          <t>-1,1; 9,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,77; 20,68</t>
+          <t>6,09; 16,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,85</t>
+          <t>-0,07; 11,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,67</t>
+          <t>2,01; 13,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 16,28</t>
+          <t>10,6; 21,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,44</t>
+          <t>1,33; 9,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,07</t>
+          <t>2,2; 9,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,11</t>
+          <t>9,77; 17,07</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>9,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>11,19%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,16; 18,8</t>
+          <t>-1,45; 14,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,48; 20,44</t>
+          <t>-1,2; 14,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,21; 33,0</t>
+          <t>8,16; 24,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 14,57</t>
+          <t>0,0; 17,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,27</t>
+          <t>2,95; 21,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,54; 23,78</t>
+          <t>15,44; 33,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,15; 14,41</t>
+          <t>1,91; 13,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,07</t>
+          <t>3,11; 14,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,78; 25,87</t>
+          <t>13,74; 25,42</t>
         </is>
       </c>
     </row>
